--- a/output/pdf_financials_xlsx/OMI.xlsx
+++ b/output/pdf_financials_xlsx/OMI.xlsx
@@ -1266,7 +1266,7 @@
         <v>-3.158</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.235</v>
+        <v>-2.121</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.848</v>
@@ -1554,7 +1554,7 @@
         <v>-1.21</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.678</v>
+        <v>-2.678</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-36.867</v>
@@ -1725,7 +1725,7 @@
         <v>-1.21</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.678</v>
+        <v>-2.678</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-36.867</v>
@@ -2043,7 +2043,7 @@
         <v>-3.158</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.235</v>
+        <v>-2.121</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.848</v>
@@ -2157,7 +2157,7 @@
         <v>2.817</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>10.378</v>
+        <v>5.022</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>8.053000000000001</v>
@@ -2214,7 +2214,7 @@
         <v>6.571641860682126</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>23.46583457694569</v>
+        <v>11.35531135531136</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>21.70619946091644</v>
@@ -2285,7 +2285,7 @@
         <v>-61.68461051298289</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>17.21792890262751</v>
+        <v>-26.26119754832626</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-368.0424528301887</v>
@@ -2342,7 +2342,7 @@
         <v>-2.822749965007232</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6.055261610817166</v>
+        <v>-6.055261610817166</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-99.37196765498652</v>
@@ -5740,34 +5740,34 @@
         <v>0</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.257</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.984</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>-0.912</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-2.016</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-1.826</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>-2.125</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>-2.725</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-1.808</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>-2.159</v>
       </c>
     </row>
     <row r="92">
@@ -5815,16 +5815,16 @@
         <v>8.590999999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>10.54</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.539</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.538</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.931</v>
       </c>
     </row>
     <row r="93">
@@ -6167,7 +6167,7 @@
         <v>-1.21</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>2.585</v>
+        <v>-2.585</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-0.848</v>
@@ -7232,49 +7232,49 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-11.342</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-17.552</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-9.246</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-6.575</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-5.194</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-2.793</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-2.604</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-2.458</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.43</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.554</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-3.087</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.734</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>1.841</v>
+        <v>0.785</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.596</v>
+        <v>-0.371</v>
       </c>
     </row>
     <row r="119">
@@ -9828,7 +9828,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10006,7 +10010,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11672,7 +11680,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11766,7 +11778,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -17472,7 +17488,11 @@
           <t>Currency translation reserve (912)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -20236,7 +20256,11 @@
           <t>Currency translation reserve (890)</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -22904,7 +22928,11 @@
           <t>Currency translation reserve (984)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -31712,7 +31740,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -41138,7 +41170,11 @@
           <t>Proceeds received for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -41935,7 +41971,7 @@
         <v>-1.21</v>
       </c>
       <c r="L351" s="5" t="n">
-        <v>2.585</v>
+        <v>-2.585</v>
       </c>
       <c r="M351" s="5" t="n">
         <v>-36.845</v>
@@ -43844,7 +43880,11 @@
           <t>Exploration and evaluation expenditure assets 9</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -45625,7 +45665,7 @@
         <v>-1.21</v>
       </c>
       <c r="L391" s="5" t="n">
-        <v>2.585</v>
+        <v>-2.585</v>
       </c>
       <c r="M391" s="5" t="n">
         <v>-36.867</v>
@@ -47062,7 +47102,11 @@
           <t>Exploration and evaluation expenditure assets 8</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -49608,7 +49652,11 @@
           <t>Exploration and evaluation expenditure assets 8</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -51848,7 +51896,11 @@
           <t>Exploration and evaluation expenditure assets 9</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>
@@ -65741,7 +65793,7 @@
         </is>
       </c>
       <c r="L605" s="5" t="n">
-        <v>2.678</v>
+        <v>-2.678</v>
       </c>
       <c r="M605" s="5" t="n">
         <v>-36.867</v>
@@ -67175,7 +67227,7 @@
         <v>-1.21</v>
       </c>
       <c r="L620" s="5" t="n">
-        <v>2.585</v>
+        <v>-2.585</v>
       </c>
       <c r="M620" t="inlineStr">
         <is>
@@ -67273,7 +67325,7 @@
         <v>-1.937</v>
       </c>
       <c r="L621" s="5" t="n">
-        <v>2.678</v>
+        <v>-2.678</v>
       </c>
       <c r="M621" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OMI.xlsx
+++ b/output/pdf_financials_xlsx/OMI.xlsx
@@ -2414,13 +2414,13 @@
         <v>5.633</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>10.818</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.787</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>1.39</v>
@@ -2435,16 +2435,16 @@
         <v>6.958</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.221</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>3.748</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.328</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>4.877</v>
       </c>
     </row>
     <row r="35">
@@ -2528,13 +2528,13 @@
         <v>5.633</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>10.818</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.787</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1.39</v>
@@ -2549,16 +2549,16 @@
         <v>6.958</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.221</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>3.748</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.328</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>4.877</v>
       </c>
     </row>
     <row r="37">
@@ -3212,13 +3212,13 @@
         <v>3.776</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>14.156</v>
+        <v>3.338</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.562</v>
+        <v>1.775</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.09</v>
+        <v>1.77</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>1.67</v>
@@ -3233,16 +3233,16 @@
         <v>3.882</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.92</v>
+        <v>1.699</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.968</v>
+        <v>1.22</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.845</v>
+        <v>0.517</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.343</v>
+        <v>0.466</v>
       </c>
     </row>
     <row r="49">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">

--- a/output/pdf_financials_xlsx/OMI.xlsx
+++ b/output/pdf_financials_xlsx/OMI.xlsx
@@ -1086,10 +1086,10 @@
         <v>-0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.666</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.376</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>-0</v>
@@ -1098,28 +1098,28 @@
         <v>-0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>0.013</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>0.006</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>0.187</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>0.019</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>0.016</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-0</v>
+        <v>0.017</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="14">
@@ -2034,10 +2034,10 @@
         <v>-14.833</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.58</v>
+        <v>5.914</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-49.401</v>
+        <v>-49.777</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-3.158</v>
@@ -2046,28 +2046,28 @@
         <v>-2.121</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.848</v>
+        <v>-0.843</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.181</v>
+        <v>-1.194</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.146</v>
+        <v>-0.152</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.693</v>
+        <v>-1.88</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.111</v>
+        <v>-1.13</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.787</v>
+        <v>-1.803</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.378</v>
+        <v>-3.395</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>9.936</v>
+        <v>9.920999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -2148,10 +2148,10 @@
         <v>4.879</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>25.318</v>
+        <v>24.652</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-32.832</v>
+        <v>-33.208</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>2.817</v>
@@ -2160,28 +2160,28 @@
         <v>5.022</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8.053000000000001</v>
+        <v>8.058</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.644</v>
+        <v>1.631</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.693</v>
+        <v>-1.88</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.111</v>
+        <v>-1.13</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.787</v>
+        <v>-1.803</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.361</v>
+        <v>-3.378</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>9.958</v>
+        <v>9.943</v>
       </c>
     </row>
     <row r="30">
@@ -2205,10 +2205,10 @@
         <v>4.607872766423633</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>31.50180415577952</v>
+        <v>30.67313674256563</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-49.84514483512479</v>
+        <v>-50.41598348211574</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>6.571641860682126</v>
@@ -2217,7 +2217,7 @@
         <v>11.35531135531136</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>21.70619946091644</v>
+        <v>21.71967654986523</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -57278,7 +57278,11 @@
           <t>Net finance cost</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -60518,7 +60522,11 @@
           <t>Net finance cost</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E550" t="inlineStr">
         <is>
           <t>-</t>
@@ -74730,7 +74738,11 @@
           <t>Net finance cost 23</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E700" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OMI.xlsx
+++ b/output/pdf_financials_xlsx/OMI.xlsx
@@ -1254,7 +1254,7 @@
         <v>-1.358</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-14.825</v>
+        <v>-14.009</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>6.584</v>
@@ -1311,7 +1311,7 @@
         <v>2.555</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-1.461</v>
@@ -1553,32 +1553,48 @@
       <c r="H20" s="3" t="n">
         <v>-1.21</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>-2.678</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-36.867</v>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" s="3" t="n">
         <v>-12.213</v>
       </c>
-      <c r="L20" s="3" t="n">
-        <v>-0.146</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>-1.693</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>-1.111</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>-1.787</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>-3.378</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>9.936</v>
+      <c r="L20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1611,31 +1627,31 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.31</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-6.544</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>1.891</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>-0.171</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>0.334</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-0.044</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>12.851</v>
       </c>
     </row>
     <row r="22">
@@ -2031,7 +2047,7 @@
         <v>-1.361</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-14.833</v>
+        <v>-14.017</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>5.914</v>
@@ -2145,7 +2161,7 @@
         <v>9.289</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.879</v>
+        <v>5.695</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>24.652</v>
@@ -2202,7 +2218,7 @@
         <v>9.915776214519797</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.607872766423633</v>
+        <v>5.378527445128632</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>30.67313674256563</v>
@@ -2273,7 +2289,7 @@
         <v>-188.1443298969072</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.824826896994789</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>22.19015795868773</v>
@@ -7906,15 +7922,11 @@
       <c r="H129" s="3" t="n">
         <v>-0.418</v>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>4.432</v>
       </c>
       <c r="K129" s="3" t="n">
         <v>1.787</v>
@@ -8264,15 +8276,11 @@
       <c r="H135" s="3" t="n">
         <v>2.862</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>1.564</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>-1.876</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-4.875</v>
@@ -43504,7 +43512,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -44822,7 +44834,11 @@
           <t>Private placement 12</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -51526,7 +51542,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -55596,7 +55616,11 @@
           <t>Proceeds from the issue of shares in a private placement 10</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -56646,7 +56670,11 @@
           <t>Commission on private placement 10</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -57636,7 +57664,11 @@
           <t>Income from discontinued operations (note 6)</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -59582,7 +59614,11 @@
           <t>(Loss) income from discontinued operations (note 6)</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -61090,7 +61126,11 @@
           <t>(Loss) income from discontinued operations (note 6)</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr"/>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E556" t="inlineStr">
         <is>
           <t>-</t>
@@ -63000,7 +63040,11 @@
           <t>Income tax recovery (note 18)</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr"/>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E576" t="inlineStr">
         <is>
           <t>-</t>
@@ -65572,7 +65616,11 @@
           <t>Loss from discontinued operations 5</t>
         </is>
       </c>
-      <c r="D603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E603" t="inlineStr">
         <is>
           <t>-</t>
@@ -76486,7 +76534,11 @@
           <t>Income tax recovery 14</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr"/>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E719" t="inlineStr">
         <is>
           <t>-</t>
